--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67636_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67636_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd209da20af4a4a00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5589b8ba5ae840d0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    236.4026</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    224.7643</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    222.6681</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    224.7643</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    197.2841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    208.6742</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    199.3541</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    218.7068</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.2976</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67636_completo.xlsx
+++ b/49849_Intercuenca_Alto_Huallaga/_raw_reportes_xlsx/IDConfig_67636_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R5589b8ba5ae840d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rac1a17e132b54e14"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    236.4026</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    255.9354</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    163.2976</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    203.5515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    191.1889</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    175.7775</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    248.5256</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    254.4149</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    275.6856</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    286.6019</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    456.9886</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    201.4432</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    203.5515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    528.6344</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    187.2212</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    221.6488</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    255.9354</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    380.8166</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    334.8777</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    268.7937</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    220.6489</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    290.3949</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    356.5446</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    323.5153</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    375.6421</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    286.6019</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    241.5978</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    193.2015</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    125.1559</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    113.9318</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    187.2212</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    208.6742</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    207.2720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    211.7099</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    134.1518</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    230.3425</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    222.6681</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    205.6789</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    156.5873</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    177.6370</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    139.7135</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    195.2332</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    168.5313</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    241.5978</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    259.0343</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    257.4752</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    244.3111</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    187.2212</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
